--- a/графики/на проверку.xlsx
+++ b/графики/на проверку.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1201475-DEF8-4302-B276-718BD9DEBC3D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C856498B-4605-4ADE-9833-D7356FDCDC1F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="09,09,26" sheetId="1" r:id="rId1"/>
+    <sheet name="10,09,26" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,33 +25,81 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
   <si>
     <t>КСК</t>
   </si>
   <si>
-    <t>TSO001119509</t>
-  </si>
-  <si>
-    <t>TSO001119559</t>
-  </si>
-  <si>
     <t>НВ</t>
   </si>
   <si>
-    <t>TSO001119728</t>
-  </si>
-  <si>
-    <t>TSO001119723</t>
-  </si>
-  <si>
-    <t>TSO001119753</t>
-  </si>
-  <si>
-    <t>TSO001119761</t>
-  </si>
-  <si>
-    <t>TSO001119763</t>
+    <t>TSO001120193</t>
+  </si>
+  <si>
+    <t>ЛП</t>
+  </si>
+  <si>
+    <t>TSO001120256</t>
+  </si>
+  <si>
+    <t>TSO001120258</t>
+  </si>
+  <si>
+    <t>TSO001120260</t>
+  </si>
+  <si>
+    <t>TSO001120259</t>
+  </si>
+  <si>
+    <t>TSO001120261</t>
+  </si>
+  <si>
+    <t>TSO001120278</t>
+  </si>
+  <si>
+    <t>TSO001120279</t>
+  </si>
+  <si>
+    <t>TSO001120275</t>
+  </si>
+  <si>
+    <t>TSO001120273</t>
+  </si>
+  <si>
+    <t>TSO001120274</t>
+  </si>
+  <si>
+    <t>TSO001120277</t>
+  </si>
+  <si>
+    <t>TSO001120276</t>
+  </si>
+  <si>
+    <t>TSO001120227</t>
+  </si>
+  <si>
+    <t>TSO001120252</t>
+  </si>
+  <si>
+    <t>TSO001120255</t>
+  </si>
+  <si>
+    <t>TSO001120281</t>
+  </si>
+  <si>
+    <t>TSO001120282</t>
+  </si>
+  <si>
+    <t>TSO001120280</t>
+  </si>
+  <si>
+    <t>TSO001120284</t>
+  </si>
+  <si>
+    <t>TSO001120283</t>
+  </si>
+  <si>
+    <t>TSO001120285</t>
   </si>
 </sst>
 </file>
@@ -94,7 +142,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -121,28 +169,39 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
+      <left style="thin">
+        <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -151,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -159,17 +218,50 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -451,90 +543,257 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6">
-        <v>18021.300000000003</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="9">
+        <v>15326.64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="5">
-        <v>19042.120000000003</v>
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="10">
+        <v>12825.84</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="6">
-        <v>13638.64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="11">
+        <v>4217.8600000000006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="12">
+        <v>3859.44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="13">
+        <v>9427.0800000000017</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="14">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="10">
+        <v>15748.080000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="11">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="12">
+        <v>2004.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="13">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="13">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="13">
+        <v>998.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="14">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="5">
-        <v>21025.500000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="6">
-        <v>17783.120000000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="5">
-        <v>17540.11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="6">
-        <v>17846.140000000003</v>
+      <c r="C14" s="15">
+        <v>17582.64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="12">
+        <v>15567.38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="14">
+        <v>2315.7800000000007</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="10">
+        <v>964.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="16">
+        <v>7275.92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="11">
+        <v>9418.86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="12">
+        <v>1556.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="14">
+        <v>16165.960000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="15">
+        <v>17727.21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>